--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.47114510823479</v>
+        <v>5.926561080088154</v>
       </c>
       <c r="D2" t="n">
-        <v>35.27953847020466</v>
+        <v>5.732925001408256</v>
       </c>
       <c r="E2" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F2" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.79636246076808</v>
+        <v>4.354408899874813</v>
       </c>
       <c r="D3" t="n">
-        <v>27.75316879011313</v>
+        <v>4.509889928393385</v>
       </c>
       <c r="E3" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F3" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.66044241372469</v>
+        <v>8.394821892230262</v>
       </c>
       <c r="D4" t="n">
-        <v>50.7521332412143</v>
+        <v>8.247221651697323</v>
       </c>
       <c r="E4" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F4" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.1850109022925</v>
+        <v>6.692564271622532</v>
       </c>
       <c r="D5" t="n">
-        <v>43.76274835756568</v>
+        <v>7.111446608104423</v>
       </c>
       <c r="E5" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F5" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.16579690841417</v>
+        <v>8.151941997617303</v>
       </c>
       <c r="D6" t="n">
-        <v>49.56731983775182</v>
+        <v>8.054689473634671</v>
       </c>
       <c r="E6" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F6" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.58080907578947</v>
+        <v>4.481881474815789</v>
       </c>
       <c r="D7" t="n">
-        <v>26.80793238246414</v>
+        <v>4.356289012150424</v>
       </c>
       <c r="E7" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F7" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.4650673584761</v>
+        <v>9.338073445752366</v>
       </c>
       <c r="D8" t="n">
-        <v>57.21721517110944</v>
+        <v>9.297797465305283</v>
       </c>
       <c r="E8" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F8" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.32039551587287</v>
+        <v>4.277064271329341</v>
       </c>
       <c r="D9" t="n">
-        <v>29.69333018992633</v>
+        <v>4.825166155863029</v>
       </c>
       <c r="E9" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F9" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31043892184974</v>
+        <v>5.087946324800583</v>
       </c>
       <c r="D10" t="n">
-        <v>27.95167628731346</v>
+        <v>4.542147396688438</v>
       </c>
       <c r="E10" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F10" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.26164905337064</v>
+        <v>5.89251797117273</v>
       </c>
       <c r="D11" t="n">
-        <v>32.80770450232291</v>
+        <v>5.331251981627473</v>
       </c>
       <c r="E11" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F11" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.20962584634834</v>
+        <v>6.046564200031606</v>
       </c>
       <c r="D12" t="n">
-        <v>39.23283813111012</v>
+        <v>6.375336196305395</v>
       </c>
       <c r="E12" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F12" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.43998914457335</v>
+        <v>7.058998235993169</v>
       </c>
       <c r="D13" t="n">
-        <v>40.66146616848381</v>
+        <v>6.607488252378619</v>
       </c>
       <c r="E13" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F13" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.71805139616598</v>
+        <v>6.129183351876972</v>
       </c>
       <c r="D14" t="n">
-        <v>35.71797126617879</v>
+        <v>5.804170330754053</v>
       </c>
       <c r="E14" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F14" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.13850415699888</v>
+        <v>4.085006925512319</v>
       </c>
       <c r="D15" t="n">
-        <v>24.33844722411681</v>
+        <v>3.954997673918982</v>
       </c>
       <c r="E15" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F15" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>12.86554601367721</v>
+        <v>2.090651227222546</v>
       </c>
       <c r="D16" t="n">
-        <v>12.13609974400556</v>
+        <v>1.972116208400904</v>
       </c>
       <c r="E16" t="n">
-        <v>11.30750397210237</v>
+        <v>1.837469395466635</v>
       </c>
       <c r="F16" t="n">
-        <v>11.29886795564109</v>
+        <v>1.836066042791677</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
